--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB. CORNELLÀ.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB. CORNELLÀ.xlsx
@@ -565,13 +565,13 @@
         <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>50.6643</v>
+        <v>66.42140000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>43.2428</v>
+        <v>51.3505</v>
       </c>
       <c r="F2" t="n">
-        <v>7.4216</v>
+        <v>15.0706</v>
       </c>
       <c r="G2" t="n">
         <v>31.4743</v>
@@ -610,13 +610,13 @@
         <v>51.9611</v>
       </c>
       <c r="S2" t="n">
-        <v>-13.786</v>
+        <v>1.9709</v>
       </c>
       <c r="T2" t="n">
-        <v>-7.0999</v>
+        <v>1.0077</v>
       </c>
       <c r="U2" t="n">
-        <v>-6.6861</v>
+        <v>0.9630999999999998</v>
       </c>
       <c r="V2" t="n">
         <v>25.7483</v>
@@ -643,13 +643,13 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>45.6335</v>
+        <v>42.3456</v>
       </c>
       <c r="E3" t="n">
-        <v>23.2605</v>
+        <v>25.1202</v>
       </c>
       <c r="F3" t="n">
-        <v>22.3728</v>
+        <v>17.2256</v>
       </c>
       <c r="G3" t="n">
         <v>35.9426</v>
@@ -688,13 +688,13 @@
         <v>51.18</v>
       </c>
       <c r="S3" t="n">
-        <v>16.6751</v>
+        <v>13.3869</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9767</v>
+        <v>3.8363</v>
       </c>
       <c r="U3" t="n">
-        <v>14.6981</v>
+        <v>9.550800000000001</v>
       </c>
       <c r="V3" t="n">
         <v>1.2204</v>
@@ -721,13 +721,13 @@
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>34.1654</v>
+        <v>31.9341</v>
       </c>
       <c r="E4" t="n">
-        <v>23.9055</v>
+        <v>20.9525</v>
       </c>
       <c r="F4" t="n">
-        <v>10.2596</v>
+        <v>10.9816</v>
       </c>
       <c r="G4" t="n">
         <v>26.9638</v>
@@ -766,13 +766,13 @@
         <v>16.7995</v>
       </c>
       <c r="S4" t="n">
-        <v>6.656</v>
+        <v>4.424799999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>5.0969</v>
+        <v>2.1438</v>
       </c>
       <c r="U4" t="n">
-        <v>1.5591</v>
+        <v>2.281</v>
       </c>
       <c r="V4" t="n">
         <v>3.8661</v>
@@ -799,13 +799,13 @@
         <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>21.0893</v>
+        <v>29.4658</v>
       </c>
       <c r="E5" t="n">
-        <v>15.5938</v>
+        <v>22.1651</v>
       </c>
       <c r="F5" t="n">
-        <v>5.495200000000001</v>
+        <v>7.301</v>
       </c>
       <c r="G5" t="n">
         <v>24.6799</v>
@@ -844,13 +844,13 @@
         <v>48.6404</v>
       </c>
       <c r="S5" t="n">
-        <v>-4.8723</v>
+        <v>3.5046</v>
       </c>
       <c r="T5" t="n">
-        <v>-5.9917</v>
+        <v>0.5795000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1191</v>
+        <v>2.925</v>
       </c>
       <c r="V5" t="n">
         <v>5.579499999999999</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>A. LLORCA CASTILLO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>17.2709</v>
+        <v>7.596200000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>23.0178</v>
+        <v>3.7151</v>
       </c>
       <c r="F6" t="n">
-        <v>-5.747</v>
+        <v>3.8812</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.7091</v>
+        <v>4.708</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.0995</v>
+        <v>3.3297</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3903</v>
+        <v>1.3784</v>
       </c>
       <c r="J6" t="n">
-        <v>24.3692</v>
+        <v>5.2112</v>
       </c>
       <c r="K6" t="n">
-        <v>17.0844</v>
+        <v>3.4266</v>
       </c>
       <c r="L6" t="n">
-        <v>7.2848</v>
+        <v>1.7844</v>
       </c>
       <c r="M6" t="n">
-        <v>-26.0783</v>
+        <v>-0.5032000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-19.1839</v>
+        <v>-0.09709999999999996</v>
       </c>
       <c r="O6" t="n">
-        <v>-6.8947</v>
+        <v>-0.406</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3441</v>
+        <v>-0.3907999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>-34.9661</v>
+        <v>-5.0789</v>
       </c>
       <c r="R6" t="n">
-        <v>37.3106</v>
+        <v>4.6882</v>
       </c>
       <c r="S6" t="n">
-        <v>26.4051</v>
+        <v>0.4091</v>
       </c>
       <c r="T6" t="n">
-        <v>23.3604</v>
+        <v>-0.5725</v>
       </c>
       <c r="U6" t="n">
-        <v>3.0448</v>
+        <v>0.9817</v>
       </c>
       <c r="V6" t="n">
-        <v>-9.7691</v>
+        <v>2.8699</v>
       </c>
       <c r="W6" t="n">
-        <v>10.2543</v>
+        <v>4.1555</v>
       </c>
       <c r="X6" t="n">
-        <v>-20.0237</v>
+        <v>-1.2856</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. LLORCA CASTILLO</t>
+          <t>G. PÉREZ LAYUNTA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>5.713299999999999</v>
+        <v>3.6236</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9357</v>
+        <v>0.623600000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>3.7776</v>
+        <v>3.0001</v>
       </c>
       <c r="G7" t="n">
-        <v>4.708</v>
+        <v>2.115199999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>3.3297</v>
+        <v>5.7968</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3784</v>
+        <v>-3.6814</v>
       </c>
       <c r="J7" t="n">
-        <v>5.2112</v>
+        <v>15.2687</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4266</v>
+        <v>13.6797</v>
       </c>
       <c r="L7" t="n">
-        <v>1.7844</v>
+        <v>1.589</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5032000000000001</v>
+        <v>-13.1533</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.09709999999999996</v>
+        <v>-7.8831</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.406</v>
+        <v>-5.270300000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3907999999999999</v>
+        <v>3.7113</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5.0789</v>
+        <v>-18.7527</v>
       </c>
       <c r="R7" t="n">
-        <v>4.6882</v>
+        <v>22.4642</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4738</v>
+        <v>0.6850999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-2.3521</v>
+        <v>0.3363999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8781</v>
+        <v>0.3491</v>
       </c>
       <c r="V7" t="n">
-        <v>2.8699</v>
+        <v>-2.8882</v>
       </c>
       <c r="W7" t="n">
-        <v>4.1555</v>
+        <v>3.7714</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2856</v>
+        <v>-6.6595</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. RAMON CASTELL</t>
+          <t>L. MARTOS RUS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0307</v>
+        <v>3.255200000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8044</v>
+        <v>8.476299999999998</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2263</v>
+        <v>-5.2211</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0187</v>
+        <v>-1.7091</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4262</v>
+        <v>-2.0995</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4449</v>
+        <v>0.3903</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1633</v>
+        <v>24.3692</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1228</v>
+        <v>17.0844</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0405</v>
+        <v>7.2848</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1445</v>
+        <v>-26.0783</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.549</v>
+        <v>-19.1839</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4045</v>
+        <v>-6.8947</v>
       </c>
       <c r="P8" t="n">
-        <v>0.586</v>
+        <v>2.3441</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-34.9661</v>
       </c>
       <c r="R8" t="n">
-        <v>0.586</v>
+        <v>37.3106</v>
       </c>
       <c r="S8" t="n">
-        <v>0.426</v>
+        <v>12.3893</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6411</v>
+        <v>8.818900000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2152</v>
+        <v>3.5707</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-9.7691</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>10.2543</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-20.0237</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. DE LA PAZ GONZALEZ</t>
+          <t>M. FENÉS HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1584</v>
+        <v>1.226</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4529</v>
+        <v>4.1488</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2945</v>
+        <v>-2.9228</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3597</v>
+        <v>1.6941</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6296</v>
+        <v>-1.2586</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2698</v>
+        <v>2.9526</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6344</v>
+        <v>7.7503</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6344</v>
+        <v>5.0627</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.6877</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2747</v>
+        <v>-6.0562</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0049</v>
+        <v>-6.321099999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2698</v>
+        <v>0.2649000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1953</v>
+        <v>5.0786</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-6.0555</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1953</v>
+        <v>11.1342</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3967</v>
+        <v>-1.3364</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1816</v>
+        <v>0.1817</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2152</v>
+        <v>-1.5181</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-4.210199999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.2727</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-6.4829</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. MASLLORENS MANRIQUE</t>
+          <t>P. RAMON CASTELL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8903000000000001</v>
+        <v>1.1461</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8392000000000002</v>
+        <v>0.7033</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7295</v>
+        <v>0.4429</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0398</v>
+        <v>0.0187</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.986</v>
+        <v>-0.4262</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.05390000000000011</v>
+        <v>0.4449</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4732999999999998</v>
+        <v>0.1633</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2827000000000001</v>
+        <v>0.1228</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7561</v>
+        <v>0.0405</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5131</v>
+        <v>-0.1445</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7032</v>
+        <v>-0.549</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8099</v>
+        <v>0.4045</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.172</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9766999999999999</v>
+        <v>0.586</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9541999999999999</v>
+        <v>0.5414</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3193</v>
+        <v>0.54</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6349</v>
+        <v>0.0014</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. FENÉS HERNÁNDEZ</t>
+          <t>A. DE LA PAZ GONZALEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8987999999999998</v>
+        <v>0.4622</v>
       </c>
       <c r="E11" t="n">
-        <v>2.4298</v>
+        <v>0.675</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.3285</v>
+        <v>-0.2128</v>
       </c>
       <c r="G11" t="n">
-        <v>1.6941</v>
+        <v>0.3597</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2586</v>
+        <v>0.6296</v>
       </c>
       <c r="I11" t="n">
-        <v>2.9526</v>
+        <v>-0.2698</v>
       </c>
       <c r="J11" t="n">
-        <v>7.7503</v>
+        <v>0.6344</v>
       </c>
       <c r="K11" t="n">
-        <v>5.0627</v>
+        <v>0.6344</v>
       </c>
       <c r="L11" t="n">
-        <v>2.6877</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-6.0562</v>
+        <v>-0.2747</v>
       </c>
       <c r="N11" t="n">
-        <v>-6.321099999999999</v>
+        <v>-0.0049</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2649000000000001</v>
+        <v>-0.2698</v>
       </c>
       <c r="P11" t="n">
-        <v>5.0786</v>
+        <v>0.1953</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.0555</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>11.1342</v>
+        <v>0.1953</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.4613</v>
+        <v>-0.0929</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.5372</v>
+        <v>0.0406</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.924</v>
+        <v>-0.1335</v>
       </c>
       <c r="V11" t="n">
-        <v>-4.210199999999999</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.2727</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-6.4829</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. BORT DOMINGUEZ</t>
+          <t>A. MASLLORENS MANRIQUE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,67 +1342,67 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.6637</v>
+        <v>-1.0864</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5132</v>
+        <v>0.6974</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.177</v>
+        <v>-1.784</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5548999999999999</v>
+        <v>-1.0398</v>
       </c>
       <c r="H12" t="n">
-        <v>0.65</v>
+        <v>-0.986</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0951</v>
+        <v>-0.05390000000000011</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1047</v>
+        <v>0.4732999999999998</v>
       </c>
       <c r="K12" t="n">
-        <v>1.0642</v>
+        <v>-0.2827000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0405</v>
+        <v>0.7561</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5498</v>
+        <v>-1.5131</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4142</v>
+        <v>-0.7032</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1356</v>
+        <v>-0.8099</v>
       </c>
       <c r="P12" t="n">
         <v>-0.1953</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9767</v>
+        <v>-1.172</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7814</v>
+        <v>0.9766999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1953</v>
+        <v>0.7579</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3853</v>
+        <v>0.1776</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5806</v>
+        <v>0.5804</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.8279</v>
+        <v>-0.6093</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X12" t="n">
         <v>-1.8279</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G. PÉREZ LAYUNTA</t>
+          <t>P. BORT DOMINGUEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.348899999999999</v>
+        <v>-1.7311</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.9036</v>
+        <v>0.311</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4452999999999996</v>
+        <v>-2.0421</v>
       </c>
       <c r="G13" t="n">
-        <v>2.115199999999999</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>5.7968</v>
+        <v>0.65</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.6814</v>
+        <v>-0.0951</v>
       </c>
       <c r="J13" t="n">
-        <v>15.2687</v>
+        <v>1.1047</v>
       </c>
       <c r="K13" t="n">
-        <v>13.6797</v>
+        <v>1.0642</v>
       </c>
       <c r="L13" t="n">
-        <v>1.589</v>
+        <v>0.0405</v>
       </c>
       <c r="M13" t="n">
-        <v>-13.1533</v>
+        <v>-0.5498</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.8831</v>
+        <v>-0.4142</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.270300000000001</v>
+        <v>-0.1356</v>
       </c>
       <c r="P13" t="n">
-        <v>3.7113</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q13" t="n">
-        <v>-18.7527</v>
+        <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>22.4642</v>
+        <v>0.7814</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.2875</v>
+        <v>-0.2628</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.191</v>
+        <v>0.183</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.0964</v>
+        <v>-0.4458</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.8882</v>
+        <v>-1.8279</v>
       </c>
       <c r="W13" t="n">
-        <v>3.7714</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.6595</v>
+        <v>-1.8279</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.0486</v>
+        <v>-2.7854</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1038</v>
+        <v>0.2049</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.1524</v>
+        <v>-2.9904</v>
       </c>
       <c r="G14" t="n">
         <v>-0.301</v>
@@ -1546,13 +1546,13 @@
         <v>1.3674</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2749</v>
+        <v>-1.0117</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0964</v>
+        <v>0.1975</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.3714</v>
+        <v>-1.2094</v>
       </c>
       <c r="V14" t="n">
         <v>-0.8865</v>
@@ -1579,13 +1579,13 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.2288</v>
+        <v>-3.6932</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.411</v>
+        <v>-4.2294</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1822000000000001</v>
+        <v>0.5363</v>
       </c>
       <c r="G15" t="n">
         <v>-3.5785</v>
@@ -1624,13 +1624,13 @@
         <v>0.3906</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4159</v>
+        <v>0.1197</v>
       </c>
       <c r="T15" t="n">
-        <v>0.157</v>
+        <v>0.3385</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5728</v>
+        <v>-0.2188</v>
       </c>
       <c r="V15" t="n">
         <v>1.3283</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. PINEÑO JIMENEZ</t>
+          <t>G. DI BONAVENTURA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>-5.5746</v>
+        <v>-3.9132</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.423500000000001</v>
+        <v>-1.719</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1511</v>
+        <v>-2.1942</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.8233</v>
+        <v>-1.2913</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.2316</v>
+        <v>-0.9818</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.5917</v>
+        <v>-0.3096000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.51</v>
+        <v>6.1183</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3504</v>
+        <v>6.2881</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.8604</v>
+        <v>-0.1698000000000002</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3133</v>
+        <v>-7.4095</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.582</v>
+        <v>-7.2699</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2687</v>
+        <v>-0.1396999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.3674</v>
+        <v>2.7347</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.1255</v>
+        <v>-8.0091</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7581</v>
+        <v>10.7439</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9294</v>
+        <v>-1.8007</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2120000000000001</v>
+        <v>-0.8823999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.1414</v>
+        <v>-0.9183000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.4545</v>
+        <v>-3.5558</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.054</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.4545</v>
+        <v>-4.610099999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. DI BONAVENTURA</t>
+          <t>P. MARTÍNEZ FERIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D17" t="n">
-        <v>-7.1126</v>
+        <v>-5.311299999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.3975</v>
+        <v>-0.9353999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.7153</v>
+        <v>-4.3759</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.2913</v>
+        <v>-5.273700000000002</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9818</v>
+        <v>-3.9503</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3096000000000001</v>
+        <v>-1.3237</v>
       </c>
       <c r="J17" t="n">
-        <v>6.1183</v>
+        <v>6.0002</v>
       </c>
       <c r="K17" t="n">
-        <v>6.2881</v>
+        <v>3.541700000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1698000000000002</v>
+        <v>2.4586</v>
       </c>
       <c r="M17" t="n">
-        <v>-7.4095</v>
+        <v>-11.274</v>
       </c>
       <c r="N17" t="n">
-        <v>-7.2699</v>
+        <v>-7.4919</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1396999999999999</v>
+        <v>-3.7822</v>
       </c>
       <c r="P17" t="n">
-        <v>2.7347</v>
+        <v>8.7902</v>
       </c>
       <c r="Q17" t="n">
-        <v>-8.0091</v>
+        <v>-7.6183</v>
       </c>
       <c r="R17" t="n">
-        <v>10.7439</v>
+        <v>16.4086</v>
       </c>
       <c r="S17" t="n">
-        <v>-5.0002</v>
+        <v>-0.4621</v>
       </c>
       <c r="T17" t="n">
-        <v>-2.5608</v>
+        <v>-0.8132000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-2.4396</v>
+        <v>0.351</v>
       </c>
       <c r="V17" t="n">
-        <v>-3.5558</v>
+        <v>-8.3658</v>
       </c>
       <c r="W17" t="n">
-        <v>1.054</v>
+        <v>1.4958</v>
       </c>
       <c r="X17" t="n">
-        <v>-4.610099999999999</v>
+        <v>-9.861599999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>J. PINEÑO JIMENEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>-7.3209</v>
+        <v>-5.788500000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>-20.7308</v>
+        <v>-4.8279</v>
       </c>
       <c r="F18" t="n">
-        <v>13.4101</v>
+        <v>-0.9605999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>-20.8729</v>
+        <v>-2.8233</v>
       </c>
       <c r="H18" t="n">
-        <v>-12.965</v>
+        <v>-1.2316</v>
       </c>
       <c r="I18" t="n">
-        <v>-7.907800000000001</v>
+        <v>-1.5917</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.376600000000001</v>
+        <v>-1.51</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.0122</v>
+        <v>0.3504</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.3647</v>
+        <v>-1.8604</v>
       </c>
       <c r="M18" t="n">
-        <v>-17.4961</v>
+        <v>-1.3133</v>
       </c>
       <c r="N18" t="n">
-        <v>-11.9531</v>
+        <v>-1.582</v>
       </c>
       <c r="O18" t="n">
-        <v>-5.5431</v>
+        <v>0.2687</v>
       </c>
       <c r="P18" t="n">
-        <v>12.8927</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q18" t="n">
-        <v>-17.776</v>
+        <v>-3.1255</v>
       </c>
       <c r="R18" t="n">
-        <v>30.6692</v>
+        <v>1.7581</v>
       </c>
       <c r="S18" t="n">
-        <v>1.7135</v>
+        <v>-1.1431</v>
       </c>
       <c r="T18" t="n">
-        <v>-3.6783</v>
+        <v>-0.1924</v>
       </c>
       <c r="U18" t="n">
-        <v>5.3921</v>
+        <v>-0.9507</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.054</v>
+        <v>-0.4545</v>
       </c>
       <c r="W18" t="n">
-        <v>4.1005</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-5.1545</v>
+        <v>-0.4545</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. LLORENS LLAURADO</t>
+          <t>F. VIEJO ANDREU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>-8.3034</v>
+        <v>-5.862</v>
       </c>
       <c r="E19" t="n">
-        <v>-16.2016</v>
+        <v>-1.3191</v>
       </c>
       <c r="F19" t="n">
-        <v>7.8983</v>
+        <v>-4.5428</v>
       </c>
       <c r="G19" t="n">
-        <v>-9.099300000000001</v>
+        <v>-8.719899999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-12.9823</v>
+        <v>-3.7719</v>
       </c>
       <c r="I19" t="n">
-        <v>3.883</v>
+        <v>-4.9481</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.2091</v>
+        <v>1.2239</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.886900000000001</v>
+        <v>-0.03460000000000008</v>
       </c>
       <c r="L19" t="n">
-        <v>2.677299999999999</v>
+        <v>1.2584</v>
       </c>
       <c r="M19" t="n">
-        <v>-5.8902</v>
+        <v>-9.9436</v>
       </c>
       <c r="N19" t="n">
-        <v>-7.0954</v>
+        <v>-3.7372</v>
       </c>
       <c r="O19" t="n">
-        <v>1.2053</v>
+        <v>-6.2065</v>
       </c>
       <c r="P19" t="n">
-        <v>5.6647</v>
+        <v>1.3673</v>
       </c>
       <c r="Q19" t="n">
-        <v>-17.3853</v>
+        <v>-5.0789</v>
       </c>
       <c r="R19" t="n">
-        <v>23.0505</v>
+        <v>6.4462</v>
       </c>
       <c r="S19" t="n">
-        <v>3.1069</v>
+        <v>2.4868</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9525</v>
+        <v>1.0948</v>
       </c>
       <c r="U19" t="n">
-        <v>1.1544</v>
+        <v>1.3918</v>
       </c>
       <c r="V19" t="n">
-        <v>-7.9758</v>
+        <v>-0.9963000000000001</v>
       </c>
       <c r="W19" t="n">
-        <v>2.4401</v>
+        <v>1.441</v>
       </c>
       <c r="X19" t="n">
-        <v>-10.4159</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>U. FERNANDEZ RUIZ</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,76 +1966,76 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>-8.645800000000001</v>
+        <v>-5.902899999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.6379</v>
+        <v>-18.2044</v>
       </c>
       <c r="F20" t="n">
-        <v>-5.008100000000001</v>
+        <v>12.3016</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.2214</v>
+        <v>-20.8729</v>
       </c>
       <c r="H20" t="n">
-        <v>-5.7895</v>
+        <v>-12.965</v>
       </c>
       <c r="I20" t="n">
-        <v>2.568099999999999</v>
+        <v>-7.907800000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>5.8757</v>
+        <v>-3.376600000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7597</v>
+        <v>-1.0122</v>
       </c>
       <c r="L20" t="n">
-        <v>3.1161</v>
+        <v>-2.3647</v>
       </c>
       <c r="M20" t="n">
-        <v>-9.097</v>
+        <v>-17.4961</v>
       </c>
       <c r="N20" t="n">
-        <v>-8.549300000000001</v>
+        <v>-11.9531</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5476999999999996</v>
+        <v>-5.5431</v>
       </c>
       <c r="P20" t="n">
-        <v>-11.1347</v>
+        <v>12.8927</v>
       </c>
       <c r="Q20" t="n">
-        <v>-30.8639</v>
+        <v>-17.776</v>
       </c>
       <c r="R20" t="n">
-        <v>19.7295</v>
+        <v>30.6692</v>
       </c>
       <c r="S20" t="n">
-        <v>12.4834</v>
+        <v>3.1313</v>
       </c>
       <c r="T20" t="n">
-        <v>11.6538</v>
+        <v>-1.1519</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8296000000000001</v>
+        <v>4.2836</v>
       </c>
       <c r="V20" t="n">
-        <v>-6.773</v>
+        <v>-1.054</v>
       </c>
       <c r="W20" t="n">
-        <v>9.696899999999999</v>
+        <v>4.1005</v>
       </c>
       <c r="X20" t="n">
-        <v>-16.4702</v>
+        <v>-5.1545</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. VIEJO ANDREU</t>
+          <t>B. ROS FERNANDEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,76 +2044,76 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D21" t="n">
-        <v>-8.8179</v>
+        <v>-5.9721</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.624099999999999</v>
+        <v>-7.0936</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.1938</v>
+        <v>1.1219</v>
       </c>
       <c r="G21" t="n">
-        <v>-8.719899999999999</v>
+        <v>-7.302200000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.7719</v>
+        <v>-4.454800000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-4.9481</v>
+        <v>-2.8475</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2239</v>
+        <v>-0.07279999999999986</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.03460000000000008</v>
+        <v>2.365</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2584</v>
+        <v>-2.4377</v>
       </c>
       <c r="M21" t="n">
-        <v>-9.9436</v>
+        <v>-7.2293</v>
       </c>
       <c r="N21" t="n">
-        <v>-3.7372</v>
+        <v>-6.819900000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>-6.2065</v>
+        <v>-0.4096999999999997</v>
       </c>
       <c r="P21" t="n">
-        <v>1.3673</v>
+        <v>-0.1952999999999998</v>
       </c>
       <c r="Q21" t="n">
-        <v>-5.0789</v>
+        <v>-13.4786</v>
       </c>
       <c r="R21" t="n">
-        <v>6.4462</v>
+        <v>13.2832</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4691</v>
+        <v>-1.0214</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.21</v>
+        <v>-2.0178</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7409</v>
+        <v>0.9964000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9963000000000001</v>
+        <v>2.547</v>
       </c>
       <c r="W21" t="n">
-        <v>1.441</v>
+        <v>8.4755</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.4373</v>
+        <v>-5.9284</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. ROS FERNANDEZ</t>
+          <t>M. OBIOLS PUIG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2122,76 +2122,76 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.956899999999999</v>
+        <v>-6.0148</v>
       </c>
       <c r="E22" t="n">
-        <v>-8.9131</v>
+        <v>-1.0298</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.04389999999999972</v>
+        <v>-4.9851</v>
       </c>
       <c r="G22" t="n">
-        <v>-7.302200000000001</v>
+        <v>-0.8059000000000004</v>
       </c>
       <c r="H22" t="n">
-        <v>-4.454800000000001</v>
+        <v>-3.196600000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.8475</v>
+        <v>2.3909</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.07279999999999986</v>
+        <v>7.7232</v>
       </c>
       <c r="K22" t="n">
-        <v>2.365</v>
+        <v>1.8202</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.4377</v>
+        <v>5.9031</v>
       </c>
       <c r="M22" t="n">
-        <v>-7.2293</v>
+        <v>-8.5289</v>
       </c>
       <c r="N22" t="n">
-        <v>-6.819900000000001</v>
+        <v>-5.0168</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4096999999999997</v>
+        <v>-3.5122</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1952999999999998</v>
+        <v>0.3904999999999998</v>
       </c>
       <c r="Q22" t="n">
-        <v>-13.4786</v>
+        <v>-10.9391</v>
       </c>
       <c r="R22" t="n">
-        <v>13.2832</v>
+        <v>11.33</v>
       </c>
       <c r="S22" t="n">
-        <v>-4.0064</v>
+        <v>-1.6775</v>
       </c>
       <c r="T22" t="n">
-        <v>-3.8372</v>
+        <v>-0.6958</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1691999999999999</v>
+        <v>-0.9818000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>2.547</v>
+        <v>-3.9222</v>
       </c>
       <c r="W22" t="n">
-        <v>8.4755</v>
+        <v>2.8819</v>
       </c>
       <c r="X22" t="n">
-        <v>-5.9284</v>
+        <v>-6.8041</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>F. LLORENS LLAURADO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2200,76 +2200,76 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D23" t="n">
-        <v>-10.0637</v>
+        <v>-8.926599999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0789</v>
+        <v>-18.3664</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.9853</v>
+        <v>9.4399</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.273700000000002</v>
+        <v>-9.099300000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.9503</v>
+        <v>-12.9823</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.3237</v>
+        <v>3.883</v>
       </c>
       <c r="J23" t="n">
-        <v>6.0002</v>
+        <v>-3.2091</v>
       </c>
       <c r="K23" t="n">
-        <v>3.541700000000001</v>
+        <v>-5.886900000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>2.4586</v>
+        <v>2.677299999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-11.274</v>
+        <v>-5.8902</v>
       </c>
       <c r="N23" t="n">
-        <v>-7.4919</v>
+        <v>-7.0954</v>
       </c>
       <c r="O23" t="n">
-        <v>-3.7822</v>
+        <v>1.2053</v>
       </c>
       <c r="P23" t="n">
-        <v>8.7902</v>
+        <v>5.6647</v>
       </c>
       <c r="Q23" t="n">
-        <v>-7.6183</v>
+        <v>-17.3853</v>
       </c>
       <c r="R23" t="n">
-        <v>16.4086</v>
+        <v>23.0505</v>
       </c>
       <c r="S23" t="n">
-        <v>-5.2145</v>
+        <v>2.4838</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.9565</v>
+        <v>-0.2121000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.2582</v>
+        <v>2.696</v>
       </c>
       <c r="V23" t="n">
-        <v>-8.3658</v>
+        <v>-7.9758</v>
       </c>
       <c r="W23" t="n">
-        <v>1.4958</v>
+        <v>2.4401</v>
       </c>
       <c r="X23" t="n">
-        <v>-9.861599999999999</v>
+        <v>-10.4159</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. OBIOLS PUIG</t>
+          <t>P. BERMEJO JARAMILLO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2278,76 +2278,76 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.1732</v>
+        <v>-11.2782</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1215</v>
+        <v>-5.9528</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.0518</v>
+        <v>-5.3251</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.8059000000000004</v>
+        <v>-8.430099999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.196600000000001</v>
+        <v>-5.1245</v>
       </c>
       <c r="I24" t="n">
-        <v>2.3909</v>
+        <v>-3.3056</v>
       </c>
       <c r="J24" t="n">
-        <v>7.7232</v>
+        <v>-3.3463</v>
       </c>
       <c r="K24" t="n">
-        <v>1.8202</v>
+        <v>-1.6616</v>
       </c>
       <c r="L24" t="n">
-        <v>5.9031</v>
+        <v>-1.6847</v>
       </c>
       <c r="M24" t="n">
-        <v>-8.5289</v>
+        <v>-5.0835</v>
       </c>
       <c r="N24" t="n">
-        <v>-5.0168</v>
+        <v>-3.4627</v>
       </c>
       <c r="O24" t="n">
-        <v>-3.5122</v>
+        <v>-1.6208</v>
       </c>
       <c r="P24" t="n">
-        <v>0.3904999999999998</v>
+        <v>0.9766999999999999</v>
       </c>
       <c r="Q24" t="n">
-        <v>-10.9391</v>
+        <v>-2.9301</v>
       </c>
       <c r="R24" t="n">
-        <v>11.33</v>
+        <v>3.9068</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.836</v>
+        <v>-0.6108000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.7873</v>
+        <v>0.3237</v>
       </c>
       <c r="U24" t="n">
-        <v>-4.0486</v>
+        <v>-0.9344999999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.9222</v>
+        <v>-3.2141</v>
       </c>
       <c r="W24" t="n">
-        <v>2.8819</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-6.8041</v>
+        <v>-3.2141</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P. BERMEJO JARAMILLO</t>
+          <t>U. FERNANDEZ RUIZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2356,70 +2356,70 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.6757</v>
+        <v>-16.5385</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.5374</v>
+        <v>-10.8988</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.138199999999999</v>
+        <v>-5.6403</v>
       </c>
       <c r="G25" t="n">
-        <v>-8.430099999999999</v>
+        <v>-3.2214</v>
       </c>
       <c r="H25" t="n">
-        <v>-5.1245</v>
+        <v>-5.7895</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.3056</v>
+        <v>2.568099999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.3463</v>
+        <v>5.8757</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.6616</v>
+        <v>2.7597</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.6847</v>
+        <v>3.1161</v>
       </c>
       <c r="M25" t="n">
-        <v>-5.0835</v>
+        <v>-9.097</v>
       </c>
       <c r="N25" t="n">
-        <v>-3.4627</v>
+        <v>-8.549300000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.6208</v>
+        <v>-0.5476999999999996</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9766999999999999</v>
+        <v>-11.1347</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.9301</v>
+        <v>-30.8639</v>
       </c>
       <c r="R25" t="n">
-        <v>3.9068</v>
+        <v>19.7295</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.008100000000000107</v>
+        <v>4.5903</v>
       </c>
       <c r="T25" t="n">
-        <v>1.7394</v>
+        <v>4.3927</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.7474</v>
+        <v>0.1976999999999999</v>
       </c>
       <c r="V25" t="n">
-        <v>-3.2141</v>
+        <v>-6.773</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>9.696899999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>-3.2141</v>
+        <v>-16.4702</v>
       </c>
     </row>
     <row r="26">
@@ -2437,22 +2437,22 @@
         <v>26</v>
       </c>
       <c r="D26" t="n">
-        <v>77.00200000000001</v>
+        <v>102.672</v>
       </c>
       <c r="E26" t="n">
-        <v>59.1185</v>
+        <v>64.5671</v>
       </c>
       <c r="F26" t="n">
-        <v>17.88199999999999</v>
+        <v>38.1055</v>
       </c>
       <c r="G26" t="n">
         <v>54.04280000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>7.512300000000003</v>
+        <v>7.5123</v>
       </c>
       <c r="I26" t="n">
-        <v>46.53039999999999</v>
+        <v>46.5304</v>
       </c>
       <c r="J26" t="n">
         <v>268.7934</v>
@@ -2461,7 +2461,7 @@
         <v>173.5513</v>
       </c>
       <c r="L26" t="n">
-        <v>95.24199999999999</v>
+        <v>95.24200000000002</v>
       </c>
       <c r="M26" t="n">
         <v>-214.75</v>
@@ -2482,13 +2482,13 @@
         <v>385.8016</v>
       </c>
       <c r="S26" t="n">
-        <v>15.79280000000001</v>
+        <v>41.46250000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>12.2072</v>
+        <v>17.6546</v>
       </c>
       <c r="U26" t="n">
-        <v>3.584999999999999</v>
+        <v>23.8088</v>
       </c>
       <c r="V26" t="n">
         <v>-13.3432</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB. CORNELLÀ.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB. CORNELLÀ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:X30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>I. MAYO SCHWANDT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>42.3456</v>
+        <v>31.9341</v>
       </c>
       <c r="E3" t="n">
-        <v>25.1202</v>
+        <v>20.9525</v>
       </c>
       <c r="F3" t="n">
-        <v>17.2256</v>
+        <v>10.9816</v>
       </c>
       <c r="G3" t="n">
-        <v>35.9426</v>
+        <v>26.9638</v>
       </c>
       <c r="H3" t="n">
-        <v>30.5369</v>
+        <v>15.1478</v>
       </c>
       <c r="I3" t="n">
-        <v>5.4057</v>
+        <v>11.8162</v>
       </c>
       <c r="J3" t="n">
-        <v>62.4893</v>
+        <v>28.0709</v>
       </c>
       <c r="K3" t="n">
-        <v>52.4782</v>
+        <v>17.8678</v>
       </c>
       <c r="L3" t="n">
-        <v>10.0107</v>
+        <v>10.2032</v>
       </c>
       <c r="M3" t="n">
-        <v>-26.5469</v>
+        <v>-1.107</v>
       </c>
       <c r="N3" t="n">
-        <v>-21.9419</v>
+        <v>-2.7199</v>
       </c>
       <c r="O3" t="n">
-        <v>-4.6052</v>
+        <v>1.613</v>
       </c>
       <c r="P3" t="n">
-        <v>-8.204699999999999</v>
+        <v>-3.3208</v>
       </c>
       <c r="Q3" t="n">
-        <v>-59.3841</v>
+        <v>-20.1203</v>
       </c>
       <c r="R3" t="n">
-        <v>51.18</v>
+        <v>16.7995</v>
       </c>
       <c r="S3" t="n">
-        <v>13.3869</v>
+        <v>4.424799999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>3.8363</v>
+        <v>2.1438</v>
       </c>
       <c r="U3" t="n">
-        <v>9.550800000000001</v>
+        <v>2.281</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2204</v>
+        <v>3.8661</v>
       </c>
       <c r="W3" t="n">
-        <v>18.1785</v>
+        <v>10.8578</v>
       </c>
       <c r="X3" t="n">
-        <v>-16.9583</v>
+        <v>-6.9917</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. MAYO SCHWANDT</t>
+          <t>A. SAMAKE EL ALAOUI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>31.9341</v>
+        <v>29.4658</v>
       </c>
       <c r="E4" t="n">
-        <v>20.9525</v>
+        <v>22.1651</v>
       </c>
       <c r="F4" t="n">
-        <v>10.9816</v>
+        <v>7.301</v>
       </c>
       <c r="G4" t="n">
-        <v>26.9638</v>
+        <v>24.6799</v>
       </c>
       <c r="H4" t="n">
-        <v>15.1478</v>
+        <v>7.1903</v>
       </c>
       <c r="I4" t="n">
-        <v>11.8162</v>
+        <v>17.4897</v>
       </c>
       <c r="J4" t="n">
-        <v>28.0709</v>
+        <v>51.1351</v>
       </c>
       <c r="K4" t="n">
-        <v>17.8678</v>
+        <v>24.8603</v>
       </c>
       <c r="L4" t="n">
-        <v>10.2032</v>
+        <v>26.2752</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.107</v>
+        <v>-26.4556</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.7199</v>
+        <v>-17.6701</v>
       </c>
       <c r="O4" t="n">
-        <v>1.613</v>
+        <v>-8.785499999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.3208</v>
+        <v>-4.297700000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>-20.1203</v>
+        <v>-52.9376</v>
       </c>
       <c r="R4" t="n">
-        <v>16.7995</v>
+        <v>48.6404</v>
       </c>
       <c r="S4" t="n">
-        <v>4.424799999999999</v>
+        <v>3.5046</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1438</v>
+        <v>0.5795000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>2.281</v>
+        <v>2.925</v>
       </c>
       <c r="V4" t="n">
-        <v>3.8661</v>
+        <v>5.579499999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>10.8578</v>
+        <v>23.388</v>
       </c>
       <c r="X4" t="n">
-        <v>-6.9917</v>
+        <v>-17.8087</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. SAMAKE EL ALAOUI</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
-        <v>29.4658</v>
+        <v>21.7055</v>
       </c>
       <c r="E5" t="n">
-        <v>22.1651</v>
+        <v>21.7055</v>
       </c>
       <c r="F5" t="n">
-        <v>7.301</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>24.6799</v>
+        <v>21.7055</v>
       </c>
       <c r="H5" t="n">
-        <v>7.1903</v>
+        <v>13.8147</v>
       </c>
       <c r="I5" t="n">
-        <v>17.4897</v>
+        <v>7.891</v>
       </c>
       <c r="J5" t="n">
-        <v>51.1351</v>
+        <v>21.7055</v>
       </c>
       <c r="K5" t="n">
-        <v>24.8603</v>
+        <v>13.8147</v>
       </c>
       <c r="L5" t="n">
-        <v>26.2752</v>
+        <v>7.891</v>
       </c>
       <c r="M5" t="n">
-        <v>-26.4556</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-17.6701</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-8.785499999999999</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-4.297700000000001</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-52.9376</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>48.6404</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.5046</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5795000000000001</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.925</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>5.579499999999999</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>23.388</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-17.8087</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. LLORCA CASTILLO</t>
+          <t>R. PEREZ GALINDO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>7.596200000000001</v>
+        <v>20.6403</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7151</v>
+        <v>3.414799999999998</v>
       </c>
       <c r="F6" t="n">
-        <v>3.8812</v>
+        <v>17.2256</v>
       </c>
       <c r="G6" t="n">
-        <v>4.708</v>
+        <v>14.2373</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3297</v>
+        <v>16.7227</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3784</v>
+        <v>-2.4852</v>
       </c>
       <c r="J6" t="n">
-        <v>5.2112</v>
+        <v>40.7841</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4266</v>
+        <v>38.664</v>
       </c>
       <c r="L6" t="n">
-        <v>1.7844</v>
+        <v>2.1199</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5032000000000001</v>
+        <v>-26.5469</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.09709999999999996</v>
+        <v>-21.9419</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.406</v>
+        <v>-4.6052</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3907999999999999</v>
+        <v>-8.204699999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5.0789</v>
+        <v>-59.3841</v>
       </c>
       <c r="R6" t="n">
-        <v>4.6882</v>
+        <v>51.18</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4091</v>
+        <v>13.3869</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5725</v>
+        <v>3.8363</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9817</v>
+        <v>9.550800000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>2.8699</v>
+        <v>1.2204</v>
       </c>
       <c r="W6" t="n">
-        <v>4.1555</v>
+        <v>18.1785</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2856</v>
+        <v>-16.9583</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. PÉREZ LAYUNTA</t>
+          <t>P. MARTÍNEZ FERIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>3.6236</v>
+        <v>11.9027</v>
       </c>
       <c r="E7" t="n">
-        <v>0.623600000000001</v>
+        <v>11.9027</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0001</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.115199999999999</v>
+        <v>11.9027</v>
       </c>
       <c r="H7" t="n">
-        <v>5.7968</v>
+        <v>5.8329</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.6814</v>
+        <v>6.07</v>
       </c>
       <c r="J7" t="n">
-        <v>15.2687</v>
+        <v>11.9027</v>
       </c>
       <c r="K7" t="n">
-        <v>13.6797</v>
+        <v>5.8329</v>
       </c>
       <c r="L7" t="n">
-        <v>1.589</v>
+        <v>6.07</v>
       </c>
       <c r="M7" t="n">
-        <v>-13.1533</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.8831</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-5.270300000000001</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.7113</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-18.7527</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>22.4642</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6850999999999999</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3363999999999999</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3491</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.8882</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.7714</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-6.6595</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>G. PÉREZ LAYUNTA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>3.255200000000001</v>
+        <v>7.625900000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>8.476299999999998</v>
+        <v>7.625900000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.2211</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7091</v>
+        <v>7.625900000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.0995</v>
+        <v>3.377</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3903</v>
+        <v>4.249</v>
       </c>
       <c r="J8" t="n">
-        <v>24.3692</v>
+        <v>7.625900000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>17.0844</v>
+        <v>3.377</v>
       </c>
       <c r="L8" t="n">
-        <v>7.2848</v>
+        <v>4.249</v>
       </c>
       <c r="M8" t="n">
-        <v>-26.0783</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-19.1839</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-6.8947</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3441</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-34.9661</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>37.3106</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>12.3893</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>8.818900000000001</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>3.5707</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-9.7691</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>10.2543</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-20.0237</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. FENÉS HERNÁNDEZ</t>
+          <t>A. LLORCA CASTILLO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>1.226</v>
+        <v>7.596200000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>4.1488</v>
+        <v>3.7151</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.9228</v>
+        <v>3.8812</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6941</v>
+        <v>4.708</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2586</v>
+        <v>3.3297</v>
       </c>
       <c r="I9" t="n">
-        <v>2.9526</v>
+        <v>1.3784</v>
       </c>
       <c r="J9" t="n">
-        <v>7.7503</v>
+        <v>5.2112</v>
       </c>
       <c r="K9" t="n">
-        <v>5.0627</v>
+        <v>3.4266</v>
       </c>
       <c r="L9" t="n">
-        <v>2.6877</v>
+        <v>1.7844</v>
       </c>
       <c r="M9" t="n">
-        <v>-6.0562</v>
+        <v>-0.5032000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-6.321099999999999</v>
+        <v>-0.09709999999999996</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2649000000000001</v>
+        <v>-0.406</v>
       </c>
       <c r="P9" t="n">
-        <v>5.0786</v>
+        <v>-0.3907999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>-6.0555</v>
+        <v>-5.0789</v>
       </c>
       <c r="R9" t="n">
-        <v>11.1342</v>
+        <v>4.6882</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3364</v>
+        <v>0.4091</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1817</v>
+        <v>-0.5725</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.5181</v>
+        <v>0.9817</v>
       </c>
       <c r="V9" t="n">
-        <v>-4.210199999999999</v>
+        <v>2.8699</v>
       </c>
       <c r="W9" t="n">
-        <v>2.2727</v>
+        <v>4.1555</v>
       </c>
       <c r="X9" t="n">
-        <v>-6.4829</v>
+        <v>-1.2856</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. RAMON CASTELL</t>
+          <t>L. MARTOS RUS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1461</v>
+        <v>3.255200000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7033</v>
+        <v>8.476299999999998</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4429</v>
+        <v>-5.2211</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0187</v>
+        <v>-1.7091</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4262</v>
+        <v>-2.0995</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4449</v>
+        <v>0.3903</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1633</v>
+        <v>24.3692</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1228</v>
+        <v>17.0844</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0405</v>
+        <v>7.2848</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1445</v>
+        <v>-26.0783</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.549</v>
+        <v>-19.1839</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4045</v>
+        <v>-6.8947</v>
       </c>
       <c r="P10" t="n">
-        <v>0.586</v>
+        <v>2.3441</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-34.9661</v>
       </c>
       <c r="R10" t="n">
-        <v>0.586</v>
+        <v>37.3106</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5414</v>
+        <v>12.3893</v>
       </c>
       <c r="T10" t="n">
-        <v>0.54</v>
+        <v>8.818900000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0014</v>
+        <v>3.5707</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-9.7691</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>10.2543</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-20.0237</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. DE LA PAZ GONZALEZ</t>
+          <t>M. FENÉS HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,61 +1264,61 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4622</v>
+        <v>2.142</v>
       </c>
       <c r="E11" t="n">
-        <v>0.675</v>
+        <v>2.142</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2128</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3597</v>
+        <v>2.142</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6296</v>
+        <v>1.535</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2698</v>
+        <v>0.607</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6344</v>
+        <v>2.142</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6344</v>
+        <v>1.535</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.607</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2747</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0049</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2698</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0929</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0406</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1335</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. MASLLORENS MANRIQUE</t>
+          <t>P. RAMON CASTELL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0864</v>
+        <v>1.1461</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6974</v>
+        <v>0.7033</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.784</v>
+        <v>0.4429</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.0398</v>
+        <v>0.0187</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.986</v>
+        <v>-0.4262</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.05390000000000011</v>
+        <v>0.4449</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4732999999999998</v>
+        <v>0.1633</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2827000000000001</v>
+        <v>0.1228</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7561</v>
+        <v>0.0405</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.5131</v>
+        <v>-0.1445</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7032</v>
+        <v>-0.549</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8099</v>
+        <v>0.4045</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.172</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9766999999999999</v>
+        <v>0.586</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7579</v>
+        <v>0.5414</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1776</v>
+        <v>0.54</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5804</v>
+        <v>0.0014</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. BORT DOMINGUEZ</t>
+          <t>A. DE LA PAZ GONZALEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.7311</v>
+        <v>0.4622</v>
       </c>
       <c r="E13" t="n">
-        <v>0.311</v>
+        <v>0.675</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0421</v>
+        <v>-0.2128</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.3597</v>
       </c>
       <c r="H13" t="n">
-        <v>0.65</v>
+        <v>0.6296</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0951</v>
+        <v>-0.2698</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1047</v>
+        <v>0.6344</v>
       </c>
       <c r="K13" t="n">
-        <v>1.0642</v>
+        <v>0.6344</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0405</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5498</v>
+        <v>-0.2747</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4142</v>
+        <v>-0.0049</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1356</v>
+        <v>-0.2698</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.1953</v>
+        <v>0.1953</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2628</v>
+        <v>-0.0929</v>
       </c>
       <c r="T13" t="n">
-        <v>0.183</v>
+        <v>0.0406</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4458</v>
+        <v>-0.1335</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. DIAZ KAUFFMANN</t>
+          <t>M. FENES HERNANDEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.7854</v>
+        <v>-0.9159000000000004</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2049</v>
+        <v>2.006900000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.9904</v>
+        <v>-2.9228</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.301</v>
+        <v>-0.4477999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-2.7936</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3093</v>
+        <v>2.3457</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3515</v>
+        <v>5.608499999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3111</v>
+        <v>3.5278</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0405</v>
+        <v>2.080699999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.6526</v>
+        <v>-6.0562</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.9215</v>
+        <v>-6.321099999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2688</v>
+        <v>0.2649000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.5861</v>
+        <v>5.0786</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9534</v>
+        <v>-6.0555</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3674</v>
+        <v>11.1342</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0117</v>
+        <v>-1.3364</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1975</v>
+        <v>0.1817</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.2094</v>
+        <v>-1.5181</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.8865</v>
+        <v>-4.210199999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6093</v>
+        <v>2.2727</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.4959</v>
+        <v>-6.4829</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. MONSALVE SANZ</t>
+          <t>A. MASLLORENS MANRIQUE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.6932</v>
+        <v>-1.0864</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.2294</v>
+        <v>0.6974</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5363</v>
+        <v>-1.784</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.5785</v>
+        <v>-1.0398</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.5554</v>
+        <v>-0.986</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.023</v>
+        <v>-0.05390000000000011</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.6145</v>
+        <v>0.4732999999999998</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.2663</v>
+        <v>-0.2827000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.3482</v>
+        <v>0.7561</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9639</v>
+        <v>-1.5131</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2890999999999999</v>
+        <v>-0.7032</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6748000000000001</v>
+        <v>-0.8099</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.5628</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9534</v>
+        <v>-1.172</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3906</v>
+        <v>0.9766999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1197</v>
+        <v>0.7579</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3385</v>
+        <v>0.1776</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2188</v>
+        <v>0.5804</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3283</v>
+        <v>-0.6093</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X15" t="n">
-        <v>1.3283</v>
+        <v>-1.8279</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. DI BONAVENTURA</t>
+          <t>P. BORT DOMINGUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-3.9132</v>
+        <v>-1.7311</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.719</v>
+        <v>0.311</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.1942</v>
+        <v>-2.0421</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.2913</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9818</v>
+        <v>0.65</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3096000000000001</v>
+        <v>-0.0951</v>
       </c>
       <c r="J16" t="n">
-        <v>6.1183</v>
+        <v>1.1047</v>
       </c>
       <c r="K16" t="n">
-        <v>6.2881</v>
+        <v>1.0642</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1698000000000002</v>
+        <v>0.0405</v>
       </c>
       <c r="M16" t="n">
-        <v>-7.4095</v>
+        <v>-0.5498</v>
       </c>
       <c r="N16" t="n">
-        <v>-7.2699</v>
+        <v>-0.4142</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1396999999999999</v>
+        <v>-0.1356</v>
       </c>
       <c r="P16" t="n">
-        <v>2.7347</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q16" t="n">
-        <v>-8.0091</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>10.7439</v>
+        <v>0.7814</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.8007</v>
+        <v>-0.2628</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8823999999999999</v>
+        <v>0.183</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9183000000000001</v>
+        <v>-0.4458</v>
       </c>
       <c r="V16" t="n">
-        <v>-3.5558</v>
+        <v>-1.8279</v>
       </c>
       <c r="W16" t="n">
-        <v>1.054</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-4.610099999999999</v>
+        <v>-1.8279</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>P. DIAZ KAUFFMANN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>-5.311299999999999</v>
+        <v>-2.7854</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9353999999999999</v>
+        <v>0.2049</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.3759</v>
+        <v>-2.9904</v>
       </c>
       <c r="G17" t="n">
-        <v>-5.273700000000002</v>
+        <v>-0.301</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.9503</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.3237</v>
+        <v>0.3093</v>
       </c>
       <c r="J17" t="n">
-        <v>6.0002</v>
+        <v>1.3515</v>
       </c>
       <c r="K17" t="n">
-        <v>3.541700000000001</v>
+        <v>1.3111</v>
       </c>
       <c r="L17" t="n">
-        <v>2.4586</v>
+        <v>0.0405</v>
       </c>
       <c r="M17" t="n">
-        <v>-11.274</v>
+        <v>-1.6526</v>
       </c>
       <c r="N17" t="n">
-        <v>-7.4919</v>
+        <v>-1.9215</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.7822</v>
+        <v>0.2688</v>
       </c>
       <c r="P17" t="n">
-        <v>8.7902</v>
+        <v>-0.5861</v>
       </c>
       <c r="Q17" t="n">
-        <v>-7.6183</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>16.4086</v>
+        <v>1.3674</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4621</v>
+        <v>-1.0117</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8132000000000001</v>
+        <v>0.1975</v>
       </c>
       <c r="U17" t="n">
-        <v>0.351</v>
+        <v>-1.2094</v>
       </c>
       <c r="V17" t="n">
-        <v>-8.3658</v>
+        <v>-0.8865</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4958</v>
+        <v>0.6093</v>
       </c>
       <c r="X17" t="n">
-        <v>-9.861599999999999</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. PINEÑO JIMENEZ</t>
+          <t>P. MONSALVE SANZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>-5.788500000000001</v>
+        <v>-3.6932</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.8279</v>
+        <v>-4.2294</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9605999999999999</v>
+        <v>0.5363</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.8233</v>
+        <v>-3.5785</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2316</v>
+        <v>-1.5554</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.5917</v>
+        <v>-2.023</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.51</v>
+        <v>-2.6145</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3504</v>
+        <v>-1.2663</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.8604</v>
+        <v>-1.3482</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3133</v>
+        <v>-0.9639</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.582</v>
+        <v>-0.2890999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2687</v>
+        <v>-0.6748000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.3674</v>
+        <v>-1.5628</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.1255</v>
+        <v>-1.9534</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7581</v>
+        <v>0.3906</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1431</v>
+        <v>0.1197</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1924</v>
+        <v>0.3385</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9507</v>
+        <v>-0.2188</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.4545</v>
+        <v>1.3283</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.4545</v>
+        <v>1.3283</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. VIEJO ANDREU</t>
+          <t>G. DI BONAVENTURA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.862</v>
+        <v>-3.9132</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3191</v>
+        <v>-1.719</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.5428</v>
+        <v>-2.1942</v>
       </c>
       <c r="G19" t="n">
-        <v>-8.719899999999999</v>
+        <v>-1.2913</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.7719</v>
+        <v>-0.9818</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.9481</v>
+        <v>-0.3096000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2239</v>
+        <v>6.1183</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.03460000000000008</v>
+        <v>6.2881</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2584</v>
+        <v>-0.1698000000000002</v>
       </c>
       <c r="M19" t="n">
-        <v>-9.9436</v>
+        <v>-7.4095</v>
       </c>
       <c r="N19" t="n">
-        <v>-3.7372</v>
+        <v>-7.2699</v>
       </c>
       <c r="O19" t="n">
-        <v>-6.2065</v>
+        <v>-0.1396999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3673</v>
+        <v>2.7347</v>
       </c>
       <c r="Q19" t="n">
-        <v>-5.0789</v>
+        <v>-8.0091</v>
       </c>
       <c r="R19" t="n">
-        <v>6.4462</v>
+        <v>10.7439</v>
       </c>
       <c r="S19" t="n">
-        <v>2.4868</v>
+        <v>-1.8007</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0948</v>
+        <v>-0.8823999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3918</v>
+        <v>-0.9183000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9963000000000001</v>
+        <v>-3.5558</v>
       </c>
       <c r="W19" t="n">
-        <v>1.441</v>
+        <v>1.054</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.4373</v>
+        <v>-4.610099999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>G. PEREZ LAYUNTA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,76 +1966,76 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.902899999999999</v>
+        <v>-4.0021</v>
       </c>
       <c r="E20" t="n">
-        <v>-18.2044</v>
+        <v>-7.0021</v>
       </c>
       <c r="F20" t="n">
-        <v>12.3016</v>
+        <v>3.0001</v>
       </c>
       <c r="G20" t="n">
-        <v>-20.8729</v>
+        <v>-5.5106</v>
       </c>
       <c r="H20" t="n">
-        <v>-12.965</v>
+        <v>2.419899999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-7.907800000000001</v>
+        <v>-7.9303</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.376600000000001</v>
+        <v>7.6431</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.0122</v>
+        <v>10.3028</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.3647</v>
+        <v>-2.6598</v>
       </c>
       <c r="M20" t="n">
-        <v>-17.4961</v>
+        <v>-13.1533</v>
       </c>
       <c r="N20" t="n">
-        <v>-11.9531</v>
+        <v>-7.8831</v>
       </c>
       <c r="O20" t="n">
-        <v>-5.5431</v>
+        <v>-5.270300000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>12.8927</v>
+        <v>3.7113</v>
       </c>
       <c r="Q20" t="n">
-        <v>-17.776</v>
+        <v>-18.7527</v>
       </c>
       <c r="R20" t="n">
-        <v>30.6692</v>
+        <v>22.4642</v>
       </c>
       <c r="S20" t="n">
-        <v>3.1313</v>
+        <v>0.6850999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1519</v>
+        <v>0.3363999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>4.2836</v>
+        <v>0.3491</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.054</v>
+        <v>-2.8882</v>
       </c>
       <c r="W20" t="n">
-        <v>4.1005</v>
+        <v>3.7714</v>
       </c>
       <c r="X20" t="n">
-        <v>-5.1545</v>
+        <v>-6.6595</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. ROS FERNANDEZ</t>
+          <t>J. PINENO JIMENEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,76 +2044,76 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.9721</v>
+        <v>-5.788500000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.0936</v>
+        <v>-4.8279</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1219</v>
+        <v>-0.9605999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>-7.302200000000001</v>
+        <v>-2.8233</v>
       </c>
       <c r="H21" t="n">
-        <v>-4.454800000000001</v>
+        <v>-1.2316</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.8475</v>
+        <v>-1.5917</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.07279999999999986</v>
+        <v>-1.51</v>
       </c>
       <c r="K21" t="n">
-        <v>2.365</v>
+        <v>0.3504</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.4377</v>
+        <v>-1.8604</v>
       </c>
       <c r="M21" t="n">
-        <v>-7.2293</v>
+        <v>-1.3133</v>
       </c>
       <c r="N21" t="n">
-        <v>-6.819900000000001</v>
+        <v>-1.582</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4096999999999997</v>
+        <v>0.2687</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1952999999999998</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q21" t="n">
-        <v>-13.4786</v>
+        <v>-3.1255</v>
       </c>
       <c r="R21" t="n">
-        <v>13.2832</v>
+        <v>1.7581</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0214</v>
+        <v>-1.1431</v>
       </c>
       <c r="T21" t="n">
-        <v>-2.0178</v>
+        <v>-0.1924</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9964000000000001</v>
+        <v>-0.9507</v>
       </c>
       <c r="V21" t="n">
-        <v>2.547</v>
+        <v>-0.4545</v>
       </c>
       <c r="W21" t="n">
-        <v>8.4755</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-5.9284</v>
+        <v>-0.4545</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. OBIOLS PUIG</t>
+          <t>F. VIEJO ANDREU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2122,76 +2122,76 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.0148</v>
+        <v>-5.862</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0298</v>
+        <v>-1.3191</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.9851</v>
+        <v>-4.5428</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8059000000000004</v>
+        <v>-8.719899999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.196600000000001</v>
+        <v>-3.7719</v>
       </c>
       <c r="I22" t="n">
-        <v>2.3909</v>
+        <v>-4.9481</v>
       </c>
       <c r="J22" t="n">
-        <v>7.7232</v>
+        <v>1.2239</v>
       </c>
       <c r="K22" t="n">
-        <v>1.8202</v>
+        <v>-0.03460000000000008</v>
       </c>
       <c r="L22" t="n">
-        <v>5.9031</v>
+        <v>1.2584</v>
       </c>
       <c r="M22" t="n">
-        <v>-8.5289</v>
+        <v>-9.9436</v>
       </c>
       <c r="N22" t="n">
-        <v>-5.0168</v>
+        <v>-3.7372</v>
       </c>
       <c r="O22" t="n">
-        <v>-3.5122</v>
+        <v>-6.2065</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3904999999999998</v>
+        <v>1.3673</v>
       </c>
       <c r="Q22" t="n">
-        <v>-10.9391</v>
+        <v>-5.0789</v>
       </c>
       <c r="R22" t="n">
-        <v>11.33</v>
+        <v>6.4462</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6775</v>
+        <v>2.4868</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6958</v>
+        <v>1.0948</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9818000000000001</v>
+        <v>1.3918</v>
       </c>
       <c r="V22" t="n">
-        <v>-3.9222</v>
+        <v>-0.9963000000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>2.8819</v>
+        <v>1.441</v>
       </c>
       <c r="X22" t="n">
-        <v>-6.8041</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F. LLORENS LLAURADO</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2200,76 +2200,76 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.926599999999999</v>
+        <v>-5.902899999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-18.3664</v>
+        <v>-18.2044</v>
       </c>
       <c r="F23" t="n">
-        <v>9.4399</v>
+        <v>12.3016</v>
       </c>
       <c r="G23" t="n">
-        <v>-9.099300000000001</v>
+        <v>-20.8729</v>
       </c>
       <c r="H23" t="n">
-        <v>-12.9823</v>
+        <v>-12.965</v>
       </c>
       <c r="I23" t="n">
-        <v>3.883</v>
+        <v>-7.907800000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.2091</v>
+        <v>-3.376600000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.886900000000001</v>
+        <v>-1.0122</v>
       </c>
       <c r="L23" t="n">
-        <v>2.677299999999999</v>
+        <v>-2.3647</v>
       </c>
       <c r="M23" t="n">
-        <v>-5.8902</v>
+        <v>-17.4961</v>
       </c>
       <c r="N23" t="n">
-        <v>-7.0954</v>
+        <v>-11.9531</v>
       </c>
       <c r="O23" t="n">
-        <v>1.2053</v>
+        <v>-5.5431</v>
       </c>
       <c r="P23" t="n">
-        <v>5.6647</v>
+        <v>12.8927</v>
       </c>
       <c r="Q23" t="n">
-        <v>-17.3853</v>
+        <v>-17.776</v>
       </c>
       <c r="R23" t="n">
-        <v>23.0505</v>
+        <v>30.6692</v>
       </c>
       <c r="S23" t="n">
-        <v>2.4838</v>
+        <v>3.1313</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2121000000000001</v>
+        <v>-1.1519</v>
       </c>
       <c r="U23" t="n">
-        <v>2.696</v>
+        <v>4.2836</v>
       </c>
       <c r="V23" t="n">
-        <v>-7.9758</v>
+        <v>-1.054</v>
       </c>
       <c r="W23" t="n">
-        <v>2.4401</v>
+        <v>4.1005</v>
       </c>
       <c r="X23" t="n">
-        <v>-10.4159</v>
+        <v>-5.1545</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. BERMEJO JARAMILLO</t>
+          <t>B. ROS FERNANDEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2278,76 +2278,76 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D24" t="n">
-        <v>-11.2782</v>
+        <v>-5.9721</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.9528</v>
+        <v>-7.0936</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.3251</v>
+        <v>1.1219</v>
       </c>
       <c r="G24" t="n">
-        <v>-8.430099999999999</v>
+        <v>-7.302200000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>-5.1245</v>
+        <v>-4.454800000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.3056</v>
+        <v>-2.8475</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.3463</v>
+        <v>-0.07279999999999986</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.6616</v>
+        <v>2.365</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.6847</v>
+        <v>-2.4377</v>
       </c>
       <c r="M24" t="n">
-        <v>-5.0835</v>
+        <v>-7.2293</v>
       </c>
       <c r="N24" t="n">
-        <v>-3.4627</v>
+        <v>-6.819900000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.6208</v>
+        <v>-0.4096999999999997</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9766999999999999</v>
+        <v>-0.1952999999999998</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.9301</v>
+        <v>-13.4786</v>
       </c>
       <c r="R24" t="n">
-        <v>3.9068</v>
+        <v>13.2832</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6108000000000001</v>
+        <v>-1.0214</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3237</v>
+        <v>-2.0178</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9344999999999999</v>
+        <v>0.9964000000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.2141</v>
+        <v>2.547</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>8.4755</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.2141</v>
+        <v>-5.9284</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>U. FERNANDEZ RUIZ</t>
+          <t>M. OBIOLS PUIG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2356,147 +2356,459 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D25" t="n">
-        <v>-16.5385</v>
+        <v>-6.0148</v>
       </c>
       <c r="E25" t="n">
-        <v>-10.8988</v>
+        <v>-1.0298</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.6403</v>
+        <v>-4.9851</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.2214</v>
+        <v>-0.8059000000000004</v>
       </c>
       <c r="H25" t="n">
-        <v>-5.7895</v>
+        <v>-3.196600000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>2.568099999999999</v>
+        <v>2.3909</v>
       </c>
       <c r="J25" t="n">
-        <v>5.8757</v>
+        <v>7.7232</v>
       </c>
       <c r="K25" t="n">
-        <v>2.7597</v>
+        <v>1.8202</v>
       </c>
       <c r="L25" t="n">
-        <v>3.1161</v>
+        <v>5.9031</v>
       </c>
       <c r="M25" t="n">
-        <v>-9.097</v>
+        <v>-8.5289</v>
       </c>
       <c r="N25" t="n">
-        <v>-8.549300000000001</v>
+        <v>-5.0168</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.5476999999999996</v>
+        <v>-3.5122</v>
       </c>
       <c r="P25" t="n">
-        <v>-11.1347</v>
+        <v>0.3904999999999998</v>
       </c>
       <c r="Q25" t="n">
-        <v>-30.8639</v>
+        <v>-10.9391</v>
       </c>
       <c r="R25" t="n">
-        <v>19.7295</v>
+        <v>11.33</v>
       </c>
       <c r="S25" t="n">
-        <v>4.5903</v>
+        <v>-1.6775</v>
       </c>
       <c r="T25" t="n">
-        <v>4.3927</v>
+        <v>-0.6958</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1976999999999999</v>
+        <v>-0.9818000000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>-6.773</v>
+        <v>-3.9222</v>
       </c>
       <c r="W25" t="n">
-        <v>9.696899999999999</v>
+        <v>2.8819</v>
       </c>
       <c r="X25" t="n">
-        <v>-16.4702</v>
+        <v>-6.8041</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>F. LLORENS LLAURADO</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>20</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-8.926599999999999</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-18.3664</v>
+      </c>
+      <c r="F26" t="n">
+        <v>9.4399</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-9.099300000000001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-12.9823</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3.883</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-3.2091</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-5.886900000000001</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2.677299999999999</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-5.8902</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-7.0954</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.2053</v>
+      </c>
+      <c r="P26" t="n">
+        <v>5.6647</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-17.3853</v>
+      </c>
+      <c r="R26" t="n">
+        <v>23.0505</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.4838</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.2121000000000001</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.696</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-7.9758</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.4401</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-10.4159</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>P. BERMEJO JARAMILLO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>7</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-11.2782</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-5.9528</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-5.3251</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-8.430099999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-5.1245</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-3.3056</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-3.3463</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-1.6616</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-1.6847</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-5.0835</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-3.4627</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-1.6208</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.9766999999999999</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R27" t="n">
+        <v>3.9068</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.6108000000000001</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.9344999999999999</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-3.2141</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-3.2141</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>U. FERNANDEZ RUIZ</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>22</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-16.5385</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-10.8988</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-5.6403</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-3.2214</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-5.7895</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.568099999999999</v>
+      </c>
+      <c r="J28" t="n">
+        <v>5.8757</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.7597</v>
+      </c>
+      <c r="L28" t="n">
+        <v>3.1161</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-9.097</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-8.549300000000001</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-0.5476999999999996</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-11.1347</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-30.8639</v>
+      </c>
+      <c r="R28" t="n">
+        <v>19.7295</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4.5903</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4.3927</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.1976999999999999</v>
+      </c>
+      <c r="V28" t="n">
+        <v>-6.773</v>
+      </c>
+      <c r="W28" t="n">
+        <v>9.696899999999999</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-16.4702</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>P. MARTINEZ FERIA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>19</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-17.2137</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-12.8378</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-4.3759</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-17.1766</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-9.782999999999999</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-7.3935</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-5.9023</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-2.291</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-3.6113</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-11.274</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-7.4919</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-3.7822</v>
+      </c>
+      <c r="P29" t="n">
+        <v>8.7902</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>-7.6183</v>
+      </c>
+      <c r="R29" t="n">
+        <v>16.4086</v>
+      </c>
+      <c r="S29" t="n">
+        <v>-0.4621</v>
+      </c>
+      <c r="T29" t="n">
+        <v>-0.8132000000000001</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="V29" t="n">
+        <v>-8.3658</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.4958</v>
+      </c>
+      <c r="X29" t="n">
+        <v>-9.861599999999999</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>--- TOTAL ---</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>CB. CORNELLÀ</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C30" t="n">
         <v>26</v>
       </c>
-      <c r="D26" t="n">
-        <v>102.672</v>
-      </c>
-      <c r="E26" t="n">
-        <v>64.5671</v>
-      </c>
-      <c r="F26" t="n">
-        <v>38.1055</v>
-      </c>
-      <c r="G26" t="n">
-        <v>54.04280000000001</v>
-      </c>
-      <c r="H26" t="n">
-        <v>7.5123</v>
-      </c>
-      <c r="I26" t="n">
-        <v>46.5304</v>
-      </c>
-      <c r="J26" t="n">
-        <v>268.7934</v>
-      </c>
-      <c r="K26" t="n">
-        <v>173.5513</v>
-      </c>
-      <c r="L26" t="n">
-        <v>95.24200000000002</v>
-      </c>
-      <c r="M26" t="n">
+      <c r="D30" t="n">
+        <v>102.6728</v>
+      </c>
+      <c r="E30" t="n">
+        <v>64.56779999999999</v>
+      </c>
+      <c r="F30" t="n">
+        <v>38.10550000000001</v>
+      </c>
+      <c r="G30" t="n">
+        <v>54.04300000000003</v>
+      </c>
+      <c r="H30" t="n">
+        <v>7.5131</v>
+      </c>
+      <c r="I30" t="n">
+        <v>46.5309</v>
+      </c>
+      <c r="J30" t="n">
+        <v>268.7944</v>
+      </c>
+      <c r="K30" t="n">
+        <v>173.5522</v>
+      </c>
+      <c r="L30" t="n">
+        <v>95.24250000000001</v>
+      </c>
+      <c r="M30" t="n">
         <v>-214.75</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N30" t="n">
         <v>-166.04</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O30" t="n">
         <v>-48.7115</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P30" t="n">
         <v>20.5089</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q30" t="n">
         <v>-365.2886</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R30" t="n">
         <v>385.8016</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S30" t="n">
         <v>41.46250000000001</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T30" t="n">
         <v>17.6546</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U30" t="n">
         <v>23.8088</v>
       </c>
-      <c r="V26" t="n">
+      <c r="V30" t="n">
         <v>-13.3432</v>
       </c>
-      <c r="W26" t="n">
+      <c r="W30" t="n">
         <v>143.4081</v>
       </c>
-      <c r="X26" t="n">
+      <c r="X30" t="n">
         <v>-156.7522</v>
       </c>
     </row>
